--- a/KatalonData/IWPTestData/EmulatorData.xlsx
+++ b/KatalonData/IWPTestData/EmulatorData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07370D1-A196-4CA7-951F-BB13CF072275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BF321E-0C57-47C1-A932-517A6CB3ADA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="2100" windowWidth="17280" windowHeight="9972" xr2:uid="{B75285DF-1640-4994-93D2-6C318038763B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B75285DF-1640-4994-93D2-6C318038763B}"/>
   </bookViews>
   <sheets>
     <sheet name="EmulatorData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="144">
   <si>
     <t>Notes</t>
   </si>
@@ -451,6 +451,12 @@
   </si>
   <si>
     <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
   </si>
 </sst>
 </file>
@@ -824,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D3E213-FD08-482B-9ECE-5B5E0D45C129}">
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF39"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1652,7 +1658,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>94</v>
       </c>
@@ -3184,6 +3190,97 @@
       </c>
       <c r="AC37" s="1" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC38" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/IWPTestData/EmulatorData.xlsx
+++ b/KatalonData/IWPTestData/EmulatorData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BF321E-0C57-47C1-A932-517A6CB3ADA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E38F7E0-3FCD-44A7-B6B0-D6758921BFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B75285DF-1640-4994-93D2-6C318038763B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="146">
   <si>
     <t>Notes</t>
   </si>
@@ -457,6 +457,12 @@
   </si>
   <si>
     <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
 </sst>
 </file>
@@ -830,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D3E213-FD08-482B-9ECE-5B5E0D45C129}">
-  <dimension ref="A1:AF39"/>
+  <dimension ref="A1:AF41"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -3283,6 +3289,87 @@
         <v>44</v>
       </c>
     </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S40" s="2"/>
+      <c r="T40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC40" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S41" s="2"/>
+      <c r="T41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC41" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
